--- a/artfynd/A 58496-2024 artfynd.xlsx
+++ b/artfynd/A 58496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126497262</v>
+        <v>126494648</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>91241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588893</v>
+        <v>588637</v>
       </c>
       <c r="R2" t="n">
-        <v>7291843</v>
+        <v>7291744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +757,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126494631</v>
+        <v>126497262</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>91259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588713</v>
+        <v>588893</v>
       </c>
       <c r="R3" t="n">
-        <v>7291770</v>
+        <v>7291843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +862,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126494648</v>
+        <v>126494631</v>
       </c>
       <c r="B4" t="n">
-        <v>91241</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588637</v>
+        <v>588713</v>
       </c>
       <c r="R4" t="n">
-        <v>7291744</v>
+        <v>7291770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126494511</v>
+        <v>126494696</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>91541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588869</v>
+        <v>588725</v>
       </c>
       <c r="R8" t="n">
-        <v>7291938</v>
+        <v>7291702</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
+          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126494696</v>
+        <v>126494511</v>
       </c>
       <c r="B9" t="n">
-        <v>91541</v>
+        <v>91263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,21 +1422,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588725</v>
+        <v>588869</v>
       </c>
       <c r="R9" t="n">
-        <v>7291702</v>
+        <v>7291938</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
+          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58496-2024 artfynd.xlsx
+++ b/artfynd/A 58496-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126494648</v>
+        <v>126494631</v>
       </c>
       <c r="B2" t="n">
-        <v>91241</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588637</v>
+        <v>588713</v>
       </c>
       <c r="R2" t="n">
-        <v>7291744</v>
+        <v>7291770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126497262</v>
+        <v>126494477</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>75075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588893</v>
+        <v>588948</v>
       </c>
       <c r="R3" t="n">
-        <v>7291843</v>
+        <v>7291998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,13 +862,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
+          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126494631</v>
+        <v>126494648</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>91241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588713</v>
+        <v>588637</v>
       </c>
       <c r="R4" t="n">
-        <v>7291770</v>
+        <v>7291744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126494477</v>
+        <v>126497262</v>
       </c>
       <c r="B5" t="n">
-        <v>75075</v>
+        <v>91259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588948</v>
+        <v>588893</v>
       </c>
       <c r="R5" t="n">
-        <v>7291998</v>
+        <v>7291843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1072,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
+          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1831,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126494620</v>
+        <v>126494618</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>91241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126494499</v>
+        <v>126494714</v>
       </c>
       <c r="B14" t="n">
-        <v>91614</v>
+        <v>91541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588911</v>
+        <v>588781</v>
       </c>
       <c r="R14" t="n">
-        <v>7291947</v>
+        <v>7291697</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
+          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126494618</v>
+        <v>126494620</v>
       </c>
       <c r="B15" t="n">
-        <v>91241</v>
+        <v>91541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126494714</v>
+        <v>126494499</v>
       </c>
       <c r="B16" t="n">
-        <v>91541</v>
+        <v>91614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588781</v>
+        <v>588911</v>
       </c>
       <c r="R16" t="n">
-        <v>7291697</v>
+        <v>7291947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
+          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 58496-2024 artfynd.xlsx
+++ b/artfynd/A 58496-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126494631</v>
+        <v>126494736</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588713</v>
+        <v>588801</v>
       </c>
       <c r="R2" t="n">
-        <v>7291770</v>
+        <v>7291717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126494648</v>
+        <v>126494574</v>
       </c>
       <c r="B3" t="n">
-        <v>91241</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588637</v>
+        <v>588823</v>
       </c>
       <c r="R3" t="n">
-        <v>7291744</v>
+        <v>7291788</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126497262</v>
+        <v>126494593</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588893</v>
+        <v>588751</v>
       </c>
       <c r="R4" t="n">
-        <v>7291843</v>
+        <v>7291780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126494477</v>
+        <v>126494620</v>
       </c>
       <c r="B5" t="n">
-        <v>75075</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588948</v>
+        <v>588713</v>
       </c>
       <c r="R5" t="n">
-        <v>7291998</v>
+        <v>7291770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1077,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
+          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1096,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126494612</v>
+        <v>126494696</v>
       </c>
       <c r="B6" t="n">
-        <v>91241</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588745</v>
+        <v>588725</v>
       </c>
       <c r="R6" t="n">
-        <v>7291766</v>
+        <v>7291702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126494716</v>
+        <v>126494714</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126494511</v>
+        <v>126494503</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588869</v>
+        <v>588911</v>
       </c>
       <c r="R8" t="n">
-        <v>7291938</v>
+        <v>7291947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126494696</v>
+        <v>126494612</v>
       </c>
       <c r="B9" t="n">
-        <v>91541</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588725</v>
+        <v>588745</v>
       </c>
       <c r="R9" t="n">
-        <v>7291702</v>
+        <v>7291766</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126494699</v>
+        <v>126494618</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588725</v>
+        <v>588713</v>
       </c>
       <c r="R10" t="n">
-        <v>7291702</v>
+        <v>7291770</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126494589</v>
+        <v>126494648</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588751</v>
+        <v>588637</v>
       </c>
       <c r="R11" t="n">
-        <v>7291780</v>
+        <v>7291744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126494541</v>
+        <v>126494589</v>
       </c>
       <c r="B12" t="n">
-        <v>82792</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588842</v>
+        <v>588751</v>
       </c>
       <c r="R12" t="n">
-        <v>7291859</v>
+        <v>7291780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126494714</v>
+        <v>126494623</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588781</v>
+        <v>588713</v>
       </c>
       <c r="R13" t="n">
-        <v>7291697</v>
+        <v>7291770</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126494499</v>
+        <v>126494699</v>
       </c>
       <c r="B14" t="n">
-        <v>91614</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588911</v>
+        <v>588725</v>
       </c>
       <c r="R14" t="n">
-        <v>7291947</v>
+        <v>7291702</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,7 +2022,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
+          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2041,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126494620</v>
+        <v>126494716</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,21 +2051,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2078,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588713</v>
+        <v>588781</v>
       </c>
       <c r="R15" t="n">
-        <v>7291770</v>
+        <v>7291697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,32 +2145,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126494618</v>
+        <v>126497262</v>
       </c>
       <c r="B16" t="n">
-        <v>91241</v>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588713</v>
+        <v>588893</v>
       </c>
       <c r="R16" t="n">
-        <v>7291770</v>
+        <v>7291843</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,6 +2227,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126494579</v>
+        <v>126494712</v>
       </c>
       <c r="B17" t="n">
-        <v>91263</v>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,21 +2262,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588823</v>
+        <v>588781</v>
       </c>
       <c r="R17" t="n">
-        <v>7291788</v>
+        <v>7291697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126494593</v>
+        <v>126494451</v>
       </c>
       <c r="B18" t="n">
-        <v>91541</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,21 +2367,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588751</v>
+        <v>589011</v>
       </c>
       <c r="R18" t="n">
-        <v>7291780</v>
+        <v>7292005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
+          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126494623</v>
+        <v>126494541</v>
       </c>
       <c r="B19" t="n">
-        <v>91245</v>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2472,21 +2472,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588713</v>
+        <v>588842</v>
       </c>
       <c r="R19" t="n">
-        <v>7291770</v>
+        <v>7291859</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,32 +2566,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126494574</v>
+        <v>126494499</v>
       </c>
       <c r="B20" t="n">
-        <v>91541</v>
+        <v>92292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588823</v>
+        <v>588911</v>
       </c>
       <c r="R20" t="n">
-        <v>7291788</v>
+        <v>7291947</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
+          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126494712</v>
+        <v>126494631</v>
       </c>
       <c r="B21" t="n">
-        <v>91699</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588781</v>
+        <v>588713</v>
       </c>
       <c r="R21" t="n">
-        <v>7291697</v>
+        <v>7291770</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126494489</v>
+        <v>126494477</v>
       </c>
       <c r="B22" t="n">
-        <v>79598</v>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,21 +2787,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588912</v>
+        <v>588948</v>
       </c>
       <c r="R22" t="n">
-        <v>7291968</v>
+        <v>7291998</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,34 +2881,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126494651</v>
+        <v>126494489</v>
       </c>
       <c r="B23" t="n">
-        <v>97246</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>224358</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2916,10 +2919,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588637</v>
+        <v>588912</v>
       </c>
       <c r="R23" t="n">
-        <v>7291744</v>
+        <v>7291968</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2965,7 +2968,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Urskogsartad, lågproduktiv barrnaturskog</t>
+          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -2983,37 +2986,34 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126494736</v>
+        <v>126494651</v>
       </c>
       <c r="B24" t="n">
-        <v>88654</v>
+        <v>97990</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>224358</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588801</v>
+        <v>588637</v>
       </c>
       <c r="R24" t="n">
-        <v>7291717</v>
+        <v>7291744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,111 +3085,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>126494503</v>
-      </c>
-      <c r="B25" t="n">
-        <v>91241</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Holmträsket, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>588911</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7291947</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv och storblockig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58496-2024 artfynd.xlsx
+++ b/artfynd/A 58496-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494736</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494574</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494593</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494696</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494714</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494503</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494612</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494618</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494589</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494623</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494699</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2142,6 +2212,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494716</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2248,6 +2323,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126497262</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2353,6 +2433,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494712</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494451</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2563,6 +2653,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494541</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494499</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2773,6 +2873,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494631</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2878,6 +2983,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494477</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2983,6 +3093,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494489</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3085,8 +3200,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>